--- a/AAII_Financials/Quarterly/ELV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>ELV</t>
   </si>
@@ -656,224 +656,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>50474000</v>
+      </c>
+      <c r="E8" s="3">
         <v>50181000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>49748000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>50711000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49776000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>48891000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45442000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45145000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>43646000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42577000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42647000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42849000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>43672000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>42172000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39929000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>39939000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38632000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38095000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>36581000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>35822000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>33851000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32385000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31760000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>31176000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>37024000</v>
+      </c>
+      <c r="E9" s="3">
         <v>35615000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>38065000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>38140000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36706000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35312000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>33500000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32949000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30572000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30546000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31334000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30606000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31604000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30786000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -901,53 +907,56 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13450000</v>
+      </c>
+      <c r="E10" s="3">
         <v>14566000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11683000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12571000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13070000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13579000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11942000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12196000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13074000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12031000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11313000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12243000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12068000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11386000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -975,8 +984,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1003,8 +1015,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1077,8 +1090,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1151,156 +1167,165 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>184000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>309000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>705000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-240000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>1144000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>39000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>427000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>5000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>655000</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E15" s="3">
         <v>112000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>164000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>162000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>147000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>155000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>180000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>122000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>162000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>116000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>217000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>212000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>221000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>235000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>247000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>225000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>166000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>129000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>135000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>136000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>90000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>80000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>92000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1324,156 +1349,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48173000</v>
+      </c>
+      <c r="E17" s="3">
         <v>47520000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48982000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48954000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47143000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45750000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44187000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42767000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40620000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39373000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>40243000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40936000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40970000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39302000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38655000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37599000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36302000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35588000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>34981000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>33625000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31293000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>30017000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>30958000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>30589000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2301000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2661000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>766000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1757000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2633000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3141000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1255000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2378000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3026000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3204000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2404000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1913000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2702000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2870000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1274000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2340000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2330000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2507000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1600000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2197000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2558000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2368000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>802000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>587000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1500,8 +1532,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1544,8 +1577,8 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1574,304 +1607,319 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2411000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2773000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>930000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1919000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2780000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3296000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1435000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2500000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3188000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3320000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2621000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2125000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2923000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3105000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1747000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2791000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2723000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2865000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1960000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2548000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2867000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2650000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1092000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>895000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E22" s="3">
         <v>357000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>367000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>351000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>341000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>344000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>340000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>280000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>265000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>259000</v>
       </c>
       <c r="N22" s="3">
         <v>259000</v>
       </c>
       <c r="O22" s="3">
+        <v>259000</v>
+      </c>
+      <c r="P22" s="3">
         <v>261000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>251000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>229000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>213000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>208000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>201000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>201000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>205000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>192000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>191000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>198000</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1937000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2304000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>215000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1406000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2292000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2797000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>606000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1373000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2986000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2939000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1001000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1654000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2441000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2619000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1045000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2127000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2122000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2306000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1400000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1996000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2353000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2176000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>611000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E24" s="3">
         <v>544000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-331000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>219000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>548000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>613000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>193000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>365000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>685000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>690000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>170000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>354000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>585000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>615000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>168000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>529000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>488000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>527000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>275000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>494000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>552000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>509000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>60000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>167000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1944,156 +1992,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1454000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1760000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>546000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1187000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1744000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2184000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>413000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1008000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2301000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2249000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>831000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1300000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1856000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2004000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>877000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1598000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1634000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1779000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1125000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1502000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1801000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1667000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>551000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>222000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1463000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1764000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>547000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1189000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1743000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2183000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>418000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1016000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2300000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2246000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>856000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1289000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1853000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1989000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>865000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1603000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1637000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1789000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1137000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1509000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1793000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>551000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>222000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2166,8 +2223,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2240,8 +2300,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2314,8 +2377,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2388,8 +2454,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2432,8 +2501,8 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2462,82 +2531,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1463000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1764000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>547000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1189000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1743000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2183000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>418000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1016000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2300000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2246000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>856000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1289000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1853000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1989000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>865000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1603000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1637000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1789000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1137000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1509000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1793000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>551000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>222000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2610,161 +2685,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1463000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1764000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>547000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1189000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1743000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2183000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>418000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1016000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2300000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2246000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>856000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1289000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1853000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1989000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>865000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1603000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1637000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1789000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1137000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1509000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1793000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>551000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>222000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2791,8 +2875,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2819,127 +2904,131 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10232000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9657000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9491000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8713000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8560000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7500000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8288000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7866000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6497000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6226000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6526000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10919000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9991000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10142000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7387000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8872000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6456000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6161000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4880000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5490000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5258000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9326000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5741000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3984000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27282000</v>
+      </c>
+      <c r="E42" s="3">
         <v>27416000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26624000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27503000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26232000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26152000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26393000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30067000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>29494000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>30041000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>29843000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>27976000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>28293000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>28028000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2967,82 +3056,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23294000</v>
+      </c>
+      <c r="E43" s="3">
         <v>23267000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21834000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22363000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23041000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21976000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18997000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18411000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19271000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17999000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18107000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16909000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16305000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16454000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11746000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10555000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10601000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11328000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9691000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9357000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9439000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9220000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8128000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8328000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3085,8 +3180,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3115,53 +3210,56 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6376000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6692000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5052000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5199000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5491000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5493000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5264000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6502000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7012000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6682000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5553000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5381000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5154000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5199000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3189,53 +3287,56 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>67184000</v>
+      </c>
+      <c r="E46" s="3">
         <v>67032000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>63001000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>63778000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>63324000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>61121000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58942000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>62846000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>62274000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>60948000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>60029000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>61185000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>59743000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>59823000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3263,230 +3364,242 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9346000</v>
+      </c>
+      <c r="E47" s="3">
         <v>9137000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10557000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11759000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11553000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11227000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9561000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10287000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7659000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7593000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6107000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6934000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6768000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6754000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>37640000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>36818000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>36938000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>37176000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>37754000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>37501000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>36338000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>36288000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>32669000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>33719000</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4645000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4657000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5131000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4657000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4641000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4617000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5219000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4505000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4450000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4451000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4943000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4821000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5152000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5015000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4920000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4797000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4691000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4585000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4547000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4520000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4416000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4161000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4129000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4042000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>39322000</v>
+      </c>
+      <c r="E49" s="3">
         <v>39433000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>39544000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39778000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>39858000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>40360000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>40371000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>36292000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>36409000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>36657000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>35590000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>35782000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>35977000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>36188000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>34698000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34917000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>35129000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>34839000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>34843000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>34933000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>34939000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>31060000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>31096000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>31184000</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3559,8 +3672,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3633,55 +3749,58 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5941000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5568000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2681000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2589000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2562000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2204000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2402000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2415000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2196000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2245000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2031000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1756000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1528000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1260000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3707,8 +3826,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3781,82 +3903,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>126438000</v>
+      </c>
+      <c r="E54" s="3">
         <v>125827000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>121494000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122749000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>121938000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119717000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116889000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116533000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>112988000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>111894000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>108928000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>110478000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>109168000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>109040000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>102755000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>103026000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>100877000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100486000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>97460000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>98060000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>96097000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>95683000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>86615000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>86574000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3883,8 +4011,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3911,275 +4040,285 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28558000</v>
+      </c>
+      <c r="E57" s="3">
         <v>28491000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28038000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25680000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27973000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27739000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26877000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26003000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25903000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27415000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28621000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27840000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27152000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>26699000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5607000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4963000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5850000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5493000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4970000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5960000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5598000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5329000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5493000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5550000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1074000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1380000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>929000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2008000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1893000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2167000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2460000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5825000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4475000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2038000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>971000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>443000</v>
       </c>
       <c r="P58" s="3">
         <v>443000</v>
       </c>
       <c r="Q58" s="3">
+        <v>443000</v>
+      </c>
+      <c r="R58" s="3">
         <v>1765000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2514000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2423000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3372000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1874000</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1024000</v>
       </c>
       <c r="W58" s="3">
         <v>1024000</v>
       </c>
       <c r="X58" s="3">
-        <v>700000</v>
+        <v>1024000</v>
       </c>
       <c r="Y58" s="3">
         <v>700000</v>
       </c>
       <c r="Z58" s="3">
+        <v>700000</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1749000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15321000</v>
+      </c>
+      <c r="E59" s="3">
         <v>15744000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11617000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14269000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13853000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13066000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11537000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13570000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10085000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12444000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11125000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14526000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13976000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14747000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2847000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5448000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2711000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2956000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2952000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2689000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>2832000</v>
       </c>
       <c r="X59" s="3">
         <v>2832000</v>
       </c>
       <c r="Y59" s="3">
+        <v>2832000</v>
+      </c>
+      <c r="Z59" s="3">
         <v>3010000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2735000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44254000</v>
+      </c>
+      <c r="E60" s="3">
         <v>45309000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>41035000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40878000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43834000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>42698000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40581000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>42033000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41813000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>44334000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41791000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43337000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41571000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>41889000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4207,156 +4346,165 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30669000</v>
+      </c>
+      <c r="E61" s="3">
         <v>30768000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31370000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31173000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28178000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28110000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30026000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24688000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24561000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21976000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23931000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24740000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25576000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25928000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22349000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21258000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21165000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19883000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>21157000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>21761000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22217000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22534000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>19335000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>19094000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4287000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3922000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2953000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4301000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4067000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4168000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2708000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3841000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2280000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2673000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1793000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2083000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1857000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1734000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2015000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1825000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2021000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2349000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2805000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2629000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2397000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1961000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2019000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2375000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4429,8 +4577,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4503,8 +4654,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4577,82 +4731,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>81416000</v>
+      </c>
+      <c r="E66" s="3">
         <v>81785000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77468000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78667000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>78087000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77097000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75463000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72654000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>70691000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71184000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>69523000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>71939000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>70856000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>71580000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>66512000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>67035000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>65065000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64511000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>61400000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>62323000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>61129000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61830000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>53416000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>52653000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4679,8 +4839,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4753,8 +4914,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4827,8 +4991,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4901,8 +5068,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4975,82 +5145,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36675000</v>
+      </c>
+      <c r="E72" s="3">
         <v>35796000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35393000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35586000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>35549000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34546000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33549000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>35157000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34575000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33088000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31749000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32103000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31608000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30707000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>29647000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>29604000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>28825000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>28058000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>27088000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>26700000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>25874000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24793000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>23802000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>24678000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5123,8 +5299,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5197,8 +5376,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5271,82 +5453,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44883000</v>
+      </c>
+      <c r="E76" s="3">
         <v>43902000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>43882000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>43953000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43722000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>42503000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41315000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43775000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>42191000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40608000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>39306000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38423000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38205000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37356000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>36243000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>35991000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35812000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35975000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>36060000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35737000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34968000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>33853000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>33199000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>33921000</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5419,161 +5607,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1463000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1764000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>547000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1189000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1743000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2183000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>418000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1016000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2300000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2246000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>856000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1289000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1853000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1989000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>865000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1603000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1637000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1789000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1137000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1509000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1793000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>551000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>222000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5600,82 +5797,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E83" s="3">
         <v>218000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-336000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>207000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>173000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>215000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-261000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>214000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>212000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>227000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-126000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>226000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>227000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>229000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>473000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>451000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>393000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>358000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>360000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>351000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>309000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>282000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>290000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5748,8 +5949,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5822,8 +6026,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5896,8 +6103,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5970,8 +6180,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6044,82 +6257,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1913000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4332000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>84000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1135000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2054000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1017000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>706000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2677000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>447000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1978000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2971000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2613000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1950000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6469000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1518000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4924000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2452000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2541000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1672000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2504000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1683000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2505000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3813000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1150000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6146,82 +6365,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-287000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-235000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-293000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-360000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-267000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-196000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-322000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-332000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-323000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-279000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-326000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-319000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-350000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-301000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-298000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-305000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-295000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-254000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-340000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-258000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-285000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-204000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-278000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-306000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6294,8 +6517,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6368,82 +6594,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1642000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>464000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1224000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-687000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>103000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1638000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-401000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-818000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2310000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1029000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-687000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-672000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3184000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>289000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1247000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2024000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1578000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-966000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1440000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4925000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2307000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>305000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>89000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6470,82 +6702,86 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E96" s="3">
         <v>376000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>377000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>381000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>385000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>386000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>373000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>378000</v>
       </c>
       <c r="K96" s="3">
         <v>378000</v>
       </c>
       <c r="L96" s="3">
+        <v>378000</v>
+      </c>
+      <c r="M96" s="3">
         <v>379000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>346000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>348000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>350000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>351000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-305000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-306000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-309000</v>
       </c>
       <c r="T96" s="3">
         <v>-309000</v>
       </c>
       <c r="U96" s="3">
+        <v>-309000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-273000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-276000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-278000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-277000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-234000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-238000</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6618,8 +6854,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6692,8 +6931,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6766,82 +7008,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1494000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2515000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>236000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>243000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-308000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1909000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1408000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-915000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>668000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>32000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-394000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-994000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1430000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-531000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-258000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-127000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>322000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1315000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-830000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-820000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3388000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2367000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-984000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6849,143 +7097,149 @@
         <v>1000</v>
       </c>
       <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>1000</v>
       </c>
       <c r="L101" s="3">
         <v>1000</v>
       </c>
       <c r="M101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N101" s="3">
         <v>2000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-6000</v>
       </c>
       <c r="O101" s="3">
         <v>-6000</v>
       </c>
       <c r="P101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-6000</v>
       </c>
       <c r="S101" s="3">
         <v>-6000</v>
       </c>
       <c r="T101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6000</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E102" s="3">
         <v>166000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>778000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>153000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1060000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-788000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>468000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1368000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>292000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4393000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>928000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-151000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2755000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1485000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2416000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>295000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1281000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-610000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>232000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4068000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3585000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1757000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2044000</v>
       </c>
     </row>
